--- a/表格模版/运达通.xlsx
+++ b/表格模版/运达通.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="14500"/>
+    <workbookView windowWidth="24280" windowHeight="12520"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -16,10 +16,6 @@
   </definedNames>
   <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
-</file>
-
-<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -241,7 +237,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="618">
   <si>
     <t>形式发票/Proforma INVOICE</t>
   </si>
@@ -293,9 +289,6 @@
     </r>
   </si>
   <si>
-    <t>GB452056904</t>
-  </si>
-  <si>
     <t>直接点击跳转对应网站</t>
   </si>
   <si>
@@ -344,9 +337,6 @@
       </rPr>
       <t>（自税必填*）</t>
     </r>
-  </si>
-  <si>
-    <t>GB452056904000</t>
   </si>
   <si>
     <t>YDT服务系统客户端</t>
@@ -4647,15 +4637,13 @@
       <c r="E5" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="42" t="s">
-        <v>10</v>
-      </c>
+      <c r="F5" s="42"/>
       <c r="G5" s="43"/>
       <c r="H5" s="44"/>
       <c r="I5" s="58"/>
       <c r="J5" s="59"/>
       <c r="K5" s="60" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L5" s="61"/>
       <c r="M5" s="61"/>
@@ -4667,25 +4655,23 @@
     </row>
     <row r="6" s="20" customFormat="1" ht="36" customHeight="1" spans="1:18">
       <c r="A6" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="38" t="s">
         <v>12</v>
-      </c>
-      <c r="B6" s="38" t="s">
-        <v>13</v>
       </c>
       <c r="C6" s="39"/>
       <c r="D6" s="40"/>
       <c r="E6" s="45" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="42" t="s">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F6" s="42"/>
       <c r="G6" s="43"/>
       <c r="H6" s="44"/>
       <c r="I6" s="62"/>
       <c r="J6" s="63"/>
       <c r="K6" s="64" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L6" s="65"/>
       <c r="M6" s="65"/>
@@ -4697,7 +4683,7 @@
     </row>
     <row r="7" s="20" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A7" s="41" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" s="42" t="str">
         <f>VLOOKUP(B6,欧洲地址库!1:65536,4,FALSE)</f>
@@ -4706,7 +4692,7 @@
       <c r="C7" s="43"/>
       <c r="D7" s="44"/>
       <c r="E7" s="45" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F7" s="42"/>
       <c r="G7" s="43"/>
@@ -4714,7 +4700,7 @@
       <c r="I7" s="62"/>
       <c r="J7" s="63"/>
       <c r="K7" s="64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L7" s="65"/>
       <c r="M7" s="65"/>
@@ -4726,7 +4712,7 @@
     </row>
     <row r="8" s="20" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A8" s="41" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8" s="42" t="str">
         <f>VLOOKUP(B6,欧洲地址库!1:65536,8,FALSE)</f>
@@ -4735,7 +4721,7 @@
       <c r="C8" s="43"/>
       <c r="D8" s="44"/>
       <c r="E8" s="45" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F8" s="42"/>
       <c r="G8" s="43"/>
@@ -4743,7 +4729,7 @@
       <c r="I8" s="58"/>
       <c r="J8" s="59"/>
       <c r="K8" s="64" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L8" s="65"/>
       <c r="M8" s="65"/>
@@ -4755,7 +4741,7 @@
     </row>
     <row r="9" s="20" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A9" s="45" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" s="42" t="str">
         <f>VLOOKUP(B6,欧洲地址库!1:65536,9,FALSE)</f>
@@ -4764,7 +4750,7 @@
       <c r="C9" s="43"/>
       <c r="D9" s="44"/>
       <c r="E9" s="51" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F9" s="52"/>
       <c r="G9" s="53"/>
@@ -4772,7 +4758,7 @@
       <c r="I9" s="62"/>
       <c r="J9" s="63"/>
       <c r="K9" s="64" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L9" s="65"/>
       <c r="M9" s="65"/>
@@ -4784,7 +4770,7 @@
     </row>
     <row r="10" s="20" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A10" s="41" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" s="42" t="str">
         <f>VLOOKUP(B6,欧洲地址库!1:65536,11,FALSE)</f>
@@ -4793,7 +4779,7 @@
       <c r="C10" s="43"/>
       <c r="D10" s="43"/>
       <c r="E10" s="54" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F10" s="42"/>
       <c r="G10" s="43"/>
@@ -4801,7 +4787,7 @@
       <c r="I10" s="58"/>
       <c r="J10" s="59"/>
       <c r="K10" s="64" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L10" s="65"/>
       <c r="M10" s="65"/>
@@ -4813,7 +4799,7 @@
     </row>
     <row r="11" s="20" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A11" s="45" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B11" s="42" t="str">
         <f>VLOOKUP(B6,欧洲地址库!1:65536,12,FALSE)</f>
@@ -4822,7 +4808,7 @@
       <c r="C11" s="43"/>
       <c r="D11" s="43"/>
       <c r="E11" s="45" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F11" s="42"/>
       <c r="G11" s="43"/>
@@ -4830,7 +4816,7 @@
       <c r="I11" s="62"/>
       <c r="J11" s="63"/>
       <c r="K11" s="64" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L11" s="65"/>
       <c r="M11" s="65"/>
@@ -4842,7 +4828,7 @@
     </row>
     <row r="12" s="20" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A12" s="41" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12" s="42" t="str">
         <f>VLOOKUP(B6,欧洲地址库!1:65536,14,FALSE)</f>
@@ -4857,7 +4843,7 @@
       <c r="I12" s="58"/>
       <c r="J12" s="59"/>
       <c r="K12" s="64" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L12" s="65"/>
       <c r="M12" s="65"/>
@@ -4869,7 +4855,7 @@
     </row>
     <row r="13" s="20" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A13" s="41" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B13" s="46" t="str">
         <f>VLOOKUP(B6,欧洲地址库!1:65536,13,FALSE)</f>
@@ -4884,7 +4870,7 @@
       <c r="I13" s="62"/>
       <c r="J13" s="63"/>
       <c r="K13" s="64" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L13" s="65"/>
       <c r="M13" s="65"/>
@@ -4896,7 +4882,7 @@
     </row>
     <row r="14" s="20" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A14" s="41" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B14" s="48">
         <v>1</v>
@@ -4910,7 +4896,7 @@
       <c r="I14" s="58"/>
       <c r="J14" s="59"/>
       <c r="K14" s="64" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L14" s="65"/>
       <c r="M14" s="65"/>
@@ -4922,58 +4908,58 @@
     </row>
     <row r="15" s="21" customFormat="1" ht="42" customHeight="1" spans="1:18">
       <c r="A15" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="50" t="s">
+      <c r="D15" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="50" t="s">
+      <c r="E15" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="50" t="s">
+      <c r="F15" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="56" t="s">
+      <c r="G15" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="56" t="s">
+      <c r="H15" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="56" t="s">
+      <c r="I15" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="57" t="s">
+      <c r="J15" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="I15" s="50" t="s">
+      <c r="K15" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="J15" s="50" t="s">
+      <c r="L15" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="50" t="s">
+      <c r="M15" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="L15" s="56" t="s">
+      <c r="N15" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="56" t="s">
+      <c r="O15" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="N15" s="67" t="s">
+      <c r="P15" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="O15" s="67" t="s">
+      <c r="Q15" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="P15" s="67" t="s">
+      <c r="R15" s="67" t="s">
         <v>53</v>
-      </c>
-      <c r="Q15" s="67" t="s">
-        <v>54</v>
-      </c>
-      <c r="R15" s="67" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="16" ht="87.95" customHeight="1" spans="1:18">
@@ -5072,7 +5058,7 @@
   <pageSetup paperSize="257" scale="32" fitToHeight="0" orientation="portrait" horizontalDpi="203" verticalDpi="203"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="B9:D12 C8:D8 B7:D7 B13" unlockedFormula="1"/>
+    <ignoredError sqref="B13 B7:D7 C8:D8 B9:D12" unlockedFormula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -5102,765 +5088,765 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="14" spans="1:14">
       <c r="A1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="J1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="K1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="16.8" spans="1:14">
       <c r="A2" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="M2" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="N2" s="16" t="s">
         <v>74</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="N2" s="16" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="16.8" spans="1:14">
       <c r="A3" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" ht="16.8" spans="1:14">
       <c r="A4" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N4" s="16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.8" spans="1:14">
       <c r="A5" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="N5" s="16" t="s">
         <v>88</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="N5" s="16" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="16.8" spans="1:14">
       <c r="A6" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N6" s="16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="16.8" spans="1:14">
       <c r="A7" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N7" s="16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.8" spans="1:14">
       <c r="A8" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N8" s="16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="16.8" spans="1:14">
       <c r="A9" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N9" s="16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="16.8" spans="1:14">
       <c r="A10" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="N10" s="16" t="s">
         <v>107</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="N10" s="16" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="17" spans="1:14">
       <c r="A11" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="N11" s="16" t="s">
         <v>112</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="N11" s="16" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="17" spans="1:14">
       <c r="A12" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="N12" s="16" t="s">
         <v>117</v>
-      </c>
-      <c r="L12" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="N12" s="16" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" ht="17" spans="1:14">
       <c r="A13" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="N13" s="16" t="s">
         <v>122</v>
-      </c>
-      <c r="L13" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="N13" s="16" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" ht="17" spans="1:14">
       <c r="A14" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="N14" s="16" t="s">
         <v>127</v>
-      </c>
-      <c r="L14" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="N14" s="16" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="16.8" spans="1:14">
       <c r="A15" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="N15" s="16" t="s">
         <v>132</v>
-      </c>
-      <c r="L15" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="N15" s="16" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="16.8" spans="1:14">
       <c r="A16" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="N16" s="16" t="s">
         <v>137</v>
-      </c>
-      <c r="L16" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="N16" s="16" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="16.8" spans="1:14">
       <c r="A17" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J17" s="15"/>
       <c r="K17" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="N17" s="16" t="s">
         <v>143</v>
-      </c>
-      <c r="L17" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="N17" s="16" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="16.8" spans="1:14">
       <c r="A18" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N18" s="16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="28" spans="1:14">
       <c r="A19" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N19" s="15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="14" spans="1:14">
       <c r="A20" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="N20" s="15" t="s">
         <v>157</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="M20" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="N20" s="15" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:14">
       <c r="A21" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="13" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J21" s="6"/>
       <c r="K21" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N21" s="13">
         <v>25261</v>
@@ -5868,37 +5854,37 @@
     </row>
     <row r="22" s="2" customFormat="1" spans="1:14">
       <c r="A22" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="13" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J22" s="6"/>
       <c r="K22" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N22" s="13">
         <v>25261</v>
@@ -5906,37 +5892,37 @@
     </row>
     <row r="23" s="2" customFormat="1" spans="1:14">
       <c r="A23" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J23" s="6"/>
       <c r="K23" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N23" s="13">
         <v>26132</v>
@@ -5944,37 +5930,37 @@
     </row>
     <row r="24" s="2" customFormat="1" spans="1:14">
       <c r="A24" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J24" s="6"/>
       <c r="K24" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N24" s="13">
         <v>33610</v>
@@ -5982,37 +5968,37 @@
     </row>
     <row r="25" s="2" customFormat="1" spans="1:14">
       <c r="A25" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J25" s="6"/>
       <c r="K25" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N25" s="13">
         <v>45410</v>
@@ -6020,37 +6006,37 @@
     </row>
     <row r="26" s="2" customFormat="1" spans="1:14">
       <c r="A26" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="13" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J26" s="6"/>
       <c r="K26" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N26" s="13">
         <v>45772</v>
@@ -6058,37 +6044,37 @@
     </row>
     <row r="27" s="2" customFormat="1" spans="1:14">
       <c r="A27" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J27" s="6"/>
       <c r="K27" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N27" s="13">
         <v>51320</v>
@@ -6096,37 +6082,37 @@
     </row>
     <row r="28" s="2" customFormat="1" spans="1:14">
       <c r="A28" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J28" s="6"/>
       <c r="K28" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N28" s="13">
         <v>59553</v>
@@ -6134,37 +6120,37 @@
     </row>
     <row r="29" s="2" customFormat="1" spans="1:14">
       <c r="A29" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J29" s="6"/>
       <c r="K29" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N29" s="17">
         <v>59353</v>
@@ -6172,37 +6158,37 @@
     </row>
     <row r="30" s="2" customFormat="1" spans="1:14">
       <c r="A30" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J30" s="6"/>
       <c r="K30" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N30" s="13">
         <v>59553</v>
@@ -6210,37 +6196,37 @@
     </row>
     <row r="31" s="2" customFormat="1" spans="1:14">
       <c r="A31" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J31" s="6"/>
       <c r="K31" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N31" s="13">
         <v>59553</v>
@@ -6248,75 +6234,75 @@
     </row>
     <row r="32" s="2" customFormat="1" spans="1:14">
       <c r="A32" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J32" s="6"/>
       <c r="K32" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="M32" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="L32" s="6" t="s">
+      <c r="N32" s="13" t="s">
         <v>209</v>
-      </c>
-      <c r="M32" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="N32" s="13" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" spans="1:14">
       <c r="A33" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J33" s="6"/>
       <c r="K33" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N33" s="17">
         <v>18196</v>
@@ -6324,37 +6310,37 @@
     </row>
     <row r="34" s="2" customFormat="1" spans="1:14">
       <c r="A34" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>217</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>219</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J34" s="6"/>
       <c r="K34" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N34" s="13">
         <v>60452</v>
@@ -6362,37 +6348,37 @@
     </row>
     <row r="35" s="2" customFormat="1" spans="1:14">
       <c r="A35" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J35" s="6"/>
       <c r="K35" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N35" s="13">
         <v>62117</v>
@@ -6400,37 +6386,37 @@
     </row>
     <row r="36" s="2" customFormat="1" spans="1:14">
       <c r="A36" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J36" s="6"/>
       <c r="K36" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N36" s="13">
         <v>71311</v>
@@ -6438,37 +6424,37 @@
     </row>
     <row r="37" s="2" customFormat="1" spans="1:14">
       <c r="A37" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="13" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J37" s="6"/>
       <c r="K37" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N37" s="13">
         <v>77380</v>
@@ -6476,37 +6462,37 @@
     </row>
     <row r="38" s="2" customFormat="1" spans="1:14">
       <c r="A38" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J38" s="6"/>
       <c r="K38" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N38" s="17">
         <v>77176</v>
@@ -6514,37 +6500,37 @@
     </row>
     <row r="39" s="2" customFormat="1" spans="1:14">
       <c r="A39" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
       <c r="H39" s="13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J39" s="6"/>
       <c r="K39" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N39" s="13">
         <v>77176</v>
@@ -6552,37 +6538,37 @@
     </row>
     <row r="40" s="2" customFormat="1" spans="1:14">
       <c r="A40" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
       <c r="H40" s="13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J40" s="6"/>
       <c r="K40" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N40" s="13">
         <v>80337</v>
@@ -6590,37 +6576,37 @@
     </row>
     <row r="41" s="2" customFormat="1" spans="1:14">
       <c r="A41" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
       <c r="H41" s="13" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J41" s="6"/>
       <c r="K41" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N41" s="13">
         <v>91225</v>
@@ -6628,37 +6614,37 @@
     </row>
     <row r="42" s="2" customFormat="1" spans="1:14">
       <c r="A42" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
       <c r="H42" s="13" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J42" s="6"/>
       <c r="K42" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N42" s="13">
         <v>13507</v>
@@ -6666,37 +6652,37 @@
     </row>
     <row r="43" s="2" customFormat="1" spans="1:14">
       <c r="A43" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
       <c r="H43" s="13" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J43" s="6"/>
       <c r="K43" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N43" s="13">
         <v>12529</v>
@@ -6704,37 +6690,37 @@
     </row>
     <row r="44" s="2" customFormat="1" spans="1:14">
       <c r="A44" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
       <c r="H44" s="13" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J44" s="6"/>
       <c r="K44" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N44" s="13">
         <v>12529</v>
@@ -6742,37 +6728,37 @@
     </row>
     <row r="45" s="2" customFormat="1" spans="1:14">
       <c r="A45" s="6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="13" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J45" s="6"/>
       <c r="K45" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N45" s="13">
         <v>14656</v>
@@ -6780,37 +6766,37 @@
     </row>
     <row r="46" s="2" customFormat="1" spans="1:14">
       <c r="A46" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
       <c r="H46" s="13" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J46" s="6"/>
       <c r="K46" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N46" s="17">
         <v>15713</v>
@@ -6818,37 +6804,37 @@
     </row>
     <row r="47" s="2" customFormat="1" spans="1:14">
       <c r="A47" s="6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="13" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J47" s="6"/>
       <c r="K47" s="6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N47" s="13">
         <v>21423</v>
@@ -6856,37 +6842,37 @@
     </row>
     <row r="48" s="2" customFormat="1" spans="1:14">
       <c r="A48" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
       <c r="H48" s="13" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J48" s="6"/>
       <c r="K48" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N48" s="13">
         <v>28832</v>
@@ -6894,37 +6880,37 @@
     </row>
     <row r="49" s="2" customFormat="1" spans="1:14">
       <c r="A49" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
       <c r="H49" s="13" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J49" s="6"/>
       <c r="K49" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N49" s="13">
         <v>36251</v>
@@ -6932,37 +6918,37 @@
     </row>
     <row r="50" s="2" customFormat="1" spans="1:14">
       <c r="A50" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
       <c r="H50" s="13" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J50" s="6"/>
       <c r="K50" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N50" s="13">
         <v>36251</v>
@@ -6970,37 +6956,37 @@
     </row>
     <row r="51" s="2" customFormat="1" spans="1:14">
       <c r="A51" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
       <c r="H51" s="13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J51" s="6"/>
       <c r="K51" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N51" s="13">
         <v>38350</v>
@@ -7008,37 +6994,37 @@
     </row>
     <row r="52" s="2" customFormat="1" spans="1:14">
       <c r="A52" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
       <c r="H52" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J52" s="6"/>
       <c r="K52" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N52" s="13">
         <v>39171</v>
@@ -7046,37 +7032,37 @@
     </row>
     <row r="53" s="2" customFormat="1" spans="1:14">
       <c r="A53" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
       <c r="H53" s="13" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J53" s="6"/>
       <c r="K53" s="6" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N53" s="13">
         <v>44145</v>
@@ -7084,37 +7070,37 @@
     </row>
     <row r="54" s="2" customFormat="1" spans="1:14">
       <c r="A54" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
       <c r="H54" s="13" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J54" s="6"/>
       <c r="K54" s="6" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N54" s="13">
         <v>44145</v>
@@ -7122,37 +7108,37 @@
     </row>
     <row r="55" s="2" customFormat="1" spans="1:14">
       <c r="A55" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="E55" s="6" t="s">
         <v>299</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>301</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
       <c r="H55" s="13" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J55" s="6"/>
       <c r="K55" s="6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N55" s="17">
         <v>58454</v>
@@ -7160,37 +7146,37 @@
     </row>
     <row r="56" s="2" customFormat="1" spans="1:14">
       <c r="A56" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
       <c r="H56" s="13" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J56" s="6"/>
       <c r="K56" s="6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N56" s="13">
         <v>46147</v>
@@ -7198,37 +7184,37 @@
     </row>
     <row r="57" s="2" customFormat="1" spans="1:14">
       <c r="A57" s="6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
       <c r="H57" s="13" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J57" s="6"/>
       <c r="K57" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N57" s="13">
         <v>47495</v>
@@ -7236,37 +7222,37 @@
     </row>
     <row r="58" s="2" customFormat="1" spans="1:14">
       <c r="A58" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
       <c r="H58" s="13" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J58" s="6"/>
       <c r="K58" s="6" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N58" s="13">
         <v>56330</v>
@@ -7274,37 +7260,37 @@
     </row>
     <row r="59" s="2" customFormat="1" spans="1:14">
       <c r="A59" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
       <c r="H59" s="13" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J59" s="6"/>
       <c r="K59" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N59" s="13">
         <v>56477</v>
@@ -7312,37 +7298,37 @@
     </row>
     <row r="60" s="2" customFormat="1" spans="1:14">
       <c r="A60" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
       <c r="H60" s="13" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J60" s="6"/>
       <c r="K60" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N60" s="13">
         <v>59302</v>
@@ -7350,37 +7336,37 @@
     </row>
     <row r="61" s="2" customFormat="1" spans="1:14">
       <c r="A61" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
       <c r="H61" s="13" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J61" s="6"/>
       <c r="K61" s="6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N61" s="13">
         <v>59368</v>
@@ -7388,37 +7374,37 @@
     </row>
     <row r="62" s="2" customFormat="1" spans="1:14">
       <c r="A62" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
       <c r="H62" s="13" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J62" s="6"/>
       <c r="K62" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N62" s="13">
         <v>63546</v>
@@ -7426,37 +7412,37 @@
     </row>
     <row r="63" s="2" customFormat="1" spans="1:14">
       <c r="A63" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
       <c r="H63" s="13" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J63" s="6"/>
       <c r="K63" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N63" s="13">
         <v>64720</v>
@@ -7464,37 +7450,37 @@
     </row>
     <row r="64" s="2" customFormat="1" spans="1:14">
       <c r="A64" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
       <c r="H64" s="13" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J64" s="6"/>
       <c r="K64" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N64" s="13">
         <v>67227</v>
@@ -7502,37 +7488,37 @@
     </row>
     <row r="65" s="2" customFormat="1" spans="1:14">
       <c r="A65" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="6"/>
       <c r="H65" s="13" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J65" s="6"/>
       <c r="K65" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N65" s="13">
         <v>67661</v>
@@ -7540,37 +7526,37 @@
     </row>
     <row r="66" s="2" customFormat="1" spans="1:14">
       <c r="A66" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
       <c r="H66" s="13" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J66" s="6"/>
       <c r="K66" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N66" s="13">
         <v>21629</v>
@@ -7578,37 +7564,37 @@
     </row>
     <row r="67" s="2" customFormat="1" spans="1:14">
       <c r="A67" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
       <c r="H67" s="13" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J67" s="6"/>
       <c r="K67" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N67" s="13">
         <v>75177</v>
@@ -7616,341 +7602,341 @@
     </row>
     <row r="68" s="2" customFormat="1" spans="1:14">
       <c r="A68" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E68" s="6" t="s">
         <v>351</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>353</v>
       </c>
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
       <c r="H68" s="13" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J68" s="6"/>
       <c r="K68" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="N68" s="13" t="s">
         <v>355</v>
-      </c>
-      <c r="L68" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="M68" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="N68" s="13" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" spans="1:14">
       <c r="A69" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
       <c r="H69" s="13" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J69" s="6"/>
       <c r="K69" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="L69" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="M69" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="N69" s="13" t="s">
         <v>355</v>
-      </c>
-      <c r="L69" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="M69" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="N69" s="13" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" spans="1:14">
       <c r="A70" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="E70" s="6" t="s">
         <v>360</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>362</v>
       </c>
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
       <c r="H70" s="13" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J70" s="6"/>
       <c r="K70" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="L70" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="M70" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="L70" s="6" t="s">
+      <c r="N70" s="13" t="s">
         <v>365</v>
-      </c>
-      <c r="M70" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="N70" s="13" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" spans="1:14">
       <c r="A71" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E71" s="6" t="s">
         <v>368</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>370</v>
       </c>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
       <c r="H71" s="13" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J71" s="6"/>
       <c r="K71" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="L71" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="M71" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="N71" s="13" t="s">
         <v>355</v>
-      </c>
-      <c r="L71" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="M71" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="N71" s="13" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" spans="1:14">
       <c r="A72" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F72" s="6"/>
       <c r="G72" s="6"/>
       <c r="H72" s="13" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J72" s="6"/>
       <c r="K72" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="N72" s="13" t="s">
         <v>375</v>
-      </c>
-      <c r="L72" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="M72" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="N72" s="13" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="73" s="2" customFormat="1" spans="1:14">
       <c r="A73" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
       <c r="H73" s="13" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J73" s="6"/>
       <c r="K73" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="L73" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="M73" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="N73" s="13" t="s">
         <v>375</v>
-      </c>
-      <c r="L73" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="M73" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="N73" s="13" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="74" s="2" customFormat="1" spans="1:14">
       <c r="A74" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
       <c r="H74" s="13" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J74" s="6"/>
       <c r="K74" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N74" s="13" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="75" s="2" customFormat="1" spans="1:14">
       <c r="A75" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="E75" s="6" t="s">
         <v>384</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="E75" s="6" t="s">
-        <v>386</v>
       </c>
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
       <c r="H75" s="13" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J75" s="6"/>
       <c r="K75" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N75" s="13" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="76" s="2" customFormat="1" spans="1:14">
       <c r="A76" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
       <c r="H76" s="13" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J76" s="6"/>
       <c r="K76" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N76" s="13">
         <v>37081</v>
@@ -7958,75 +7944,75 @@
     </row>
     <row r="77" s="2" customFormat="1" spans="1:14">
       <c r="A77" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
       <c r="H77" s="13" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J77" s="6"/>
       <c r="K77" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N77" s="13" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="78" s="2" customFormat="1" spans="1:14">
       <c r="A78" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
       <c r="H78" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J78" s="6"/>
       <c r="K78" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N78" s="13">
         <v>10037</v>
@@ -8034,37 +8020,37 @@
     </row>
     <row r="79" s="2" customFormat="1" spans="1:14">
       <c r="A79" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
       <c r="H79" s="13" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J79" s="6"/>
       <c r="K79" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N79" s="13">
         <v>13100</v>
@@ -8072,37 +8058,37 @@
     </row>
     <row r="80" s="2" customFormat="1" spans="1:14">
       <c r="A80" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="E80" s="6" t="s">
         <v>408</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>410</v>
       </c>
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
       <c r="H80" s="13" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J80" s="6"/>
       <c r="K80" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N80" s="13">
         <v>20080</v>
@@ -8110,37 +8096,37 @@
     </row>
     <row r="81" s="2" customFormat="1" spans="1:14">
       <c r="A81" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
       <c r="H81" s="13" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J81" s="6"/>
       <c r="K81" s="6" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N81" s="13">
         <v>20080</v>
@@ -8148,37 +8134,37 @@
     </row>
     <row r="82" s="2" customFormat="1" spans="1:14">
       <c r="A82" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F82" s="6"/>
       <c r="G82" s="6"/>
       <c r="H82" s="13" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J82" s="6"/>
       <c r="K82" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N82" s="13">
         <v>24050</v>
@@ -8186,37 +8172,37 @@
     </row>
     <row r="83" s="2" customFormat="1" spans="1:14">
       <c r="A83" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
       <c r="H83" s="13" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J83" s="6"/>
       <c r="K83" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N83" s="13">
         <v>27010</v>
@@ -8224,37 +8210,37 @@
     </row>
     <row r="84" s="2" customFormat="1" spans="1:14">
       <c r="A84" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="E84" s="6" t="s">
         <v>424</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>426</v>
       </c>
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
       <c r="H84" s="13" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J84" s="6"/>
       <c r="K84" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N84" s="13">
         <v>28100</v>
@@ -8262,37 +8248,37 @@
     </row>
     <row r="85" s="2" customFormat="1" spans="1:14">
       <c r="A85" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
       <c r="H85" s="13" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J85" s="6"/>
       <c r="K85" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N85" s="13">
         <v>29015</v>
@@ -8300,37 +8286,37 @@
     </row>
     <row r="86" s="2" customFormat="1" spans="1:14">
       <c r="A86" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
       <c r="H86" s="13" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J86" s="6"/>
       <c r="K86" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N86" s="13">
         <v>45020</v>
@@ -8338,37 +8324,37 @@
     </row>
     <row r="87" s="2" customFormat="1" spans="1:14">
       <c r="A87" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="E87" s="6" t="s">
         <v>437</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="E87" s="6" t="s">
-        <v>439</v>
       </c>
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
       <c r="H87" s="13" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J87" s="6"/>
       <c r="K87" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N87" s="13">
         <v>45031</v>
@@ -8376,37 +8362,37 @@
     </row>
     <row r="88" s="2" customFormat="1" spans="1:14">
       <c r="A88" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
       <c r="H88" s="13" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J88" s="6"/>
       <c r="K88" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N88" s="13">
         <v>45031</v>
@@ -8414,37 +8400,37 @@
     </row>
     <row r="89" s="2" customFormat="1" spans="1:14">
       <c r="A89" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F89" s="6"/>
       <c r="G89" s="6"/>
       <c r="H89" s="13" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J89" s="6"/>
       <c r="K89" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M89" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N89" s="17">
         <v>15122</v>
@@ -8452,37 +8438,37 @@
     </row>
     <row r="90" s="2" customFormat="1" spans="1:14">
       <c r="A90" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
       <c r="H90" s="13" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J90" s="6"/>
       <c r="K90" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N90" s="17">
         <v>80470</v>
@@ -8490,37 +8476,37 @@
     </row>
     <row r="91" s="2" customFormat="1" spans="1:14">
       <c r="A91" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F91" s="6"/>
       <c r="G91" s="6"/>
       <c r="H91" s="13" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J91" s="6"/>
       <c r="K91" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M91" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N91" s="13">
         <v>66050</v>
@@ -8528,113 +8514,113 @@
     </row>
     <row r="92" s="2" customFormat="1" spans="1:14">
       <c r="A92" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
       <c r="H92" s="13" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J92" s="6"/>
       <c r="K92" s="6" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N92" s="13" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="93" s="2" customFormat="1" spans="1:14">
       <c r="A93" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
       <c r="H93" s="13" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J93" s="6"/>
       <c r="K93" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M93" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N93" s="13" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="94" s="2" customFormat="1" spans="1:14">
       <c r="A94" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
       <c r="H94" s="13" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J94" s="6"/>
       <c r="K94" s="6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="N94" s="13">
         <v>41208</v>
@@ -8642,37 +8628,37 @@
     </row>
     <row r="95" s="2" customFormat="1" spans="1:14">
       <c r="A95" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
       <c r="H95" s="13" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J95" s="6"/>
       <c r="K95" s="6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M95" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="N95" s="13">
         <v>55020</v>
@@ -8680,37 +8666,37 @@
     </row>
     <row r="96" s="2" customFormat="1" spans="1:14">
       <c r="A96" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
       <c r="H96" s="13" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J96" s="6"/>
       <c r="K96" s="6" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="N96" s="13">
         <v>55040</v>
@@ -8718,75 +8704,75 @@
     </row>
     <row r="97" s="2" customFormat="1" spans="1:14">
       <c r="A97" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
       <c r="H97" s="13" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J97" s="6"/>
       <c r="K97" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="L97" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="M97" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="N97" s="13" t="s">
         <v>355</v>
-      </c>
-      <c r="L97" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="M97" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="N97" s="13" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="98" s="2" customFormat="1" spans="1:14">
       <c r="A98" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
       <c r="H98" s="13" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J98" s="6"/>
       <c r="K98" s="6" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="N98" s="13">
         <v>55040</v>
@@ -8794,37 +8780,37 @@
     </row>
     <row r="99" s="2" customFormat="1" spans="1:14">
       <c r="A99" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F99" s="6"/>
       <c r="G99" s="6"/>
       <c r="H99" s="13" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J99" s="6"/>
       <c r="K99" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="M99" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="N99" s="13">
         <v>59225</v>
@@ -8832,37 +8818,37 @@
     </row>
     <row r="100" s="2" customFormat="1" spans="1:14">
       <c r="A100" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F100" s="6"/>
       <c r="G100" s="6"/>
       <c r="H100" s="13" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J100" s="6"/>
       <c r="K100" s="6" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M100" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="N100" s="13">
         <v>62080</v>
@@ -8870,37 +8856,37 @@
     </row>
     <row r="101" s="2" customFormat="1" spans="1:14">
       <c r="A101" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F101" s="6"/>
       <c r="G101" s="6"/>
       <c r="H101" s="13" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J101" s="6"/>
       <c r="K101" s="6" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="L101" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M101" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="N101" s="13">
         <v>72001</v>
@@ -8908,37 +8894,37 @@
     </row>
     <row r="102" s="2" customFormat="1" spans="1:14">
       <c r="A102" s="6" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F102" s="6"/>
       <c r="G102" s="6"/>
       <c r="H102" s="13" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J102" s="6"/>
       <c r="K102" s="6" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="L102" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="N102" s="13">
         <v>93614</v>
@@ -8946,37 +8932,37 @@
     </row>
     <row r="103" s="2" customFormat="1" spans="1:14">
       <c r="A103" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F103" s="6"/>
       <c r="G103" s="6"/>
       <c r="H103" s="13" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J103" s="6"/>
       <c r="K103" s="6" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M103" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="N103" s="13">
         <v>93614</v>
@@ -8984,37 +8970,37 @@
     </row>
     <row r="104" s="2" customFormat="1" spans="1:14">
       <c r="A104" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F104" s="6"/>
       <c r="G104" s="6"/>
       <c r="H104" s="13" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J104" s="6"/>
       <c r="K104" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M104" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="N104" s="13">
         <v>95200</v>
@@ -9022,75 +9008,75 @@
     </row>
     <row r="105" s="2" customFormat="1" spans="1:14">
       <c r="A105" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F105" s="6"/>
       <c r="G105" s="6"/>
       <c r="H105" s="13" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J105" s="6"/>
       <c r="K105" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="L105" s="6" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="M105" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N105" s="13" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="106" s="2" customFormat="1" spans="1:14">
       <c r="A106" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F106" s="6"/>
       <c r="G106" s="6"/>
       <c r="H106" s="13" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J106" s="6"/>
       <c r="K106" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N106" s="13">
         <v>19208</v>
@@ -9098,37 +9084,37 @@
     </row>
     <row r="107" s="2" customFormat="1" spans="1:14">
       <c r="A107" s="6" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F107" s="6"/>
       <c r="G107" s="6"/>
       <c r="H107" s="13" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J107" s="6"/>
       <c r="K107" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M107" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N107" s="13">
         <v>28096</v>
@@ -9136,37 +9122,37 @@
     </row>
     <row r="108" s="2" customFormat="1" spans="1:14">
       <c r="A108" s="6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F108" s="6"/>
       <c r="G108" s="6"/>
       <c r="H108" s="13" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J108" s="6"/>
       <c r="K108" s="6" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="L108" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M108" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N108" s="13">
         <v>28805</v>
@@ -9174,75 +9160,75 @@
     </row>
     <row r="109" s="2" customFormat="1" spans="1:14">
       <c r="A109" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F109" s="6"/>
       <c r="G109" s="6"/>
       <c r="H109" s="13" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J109" s="6"/>
       <c r="K109" s="6" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="M109" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N109" s="13" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="110" s="2" customFormat="1" spans="1:14">
       <c r="A110" s="6" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F110" s="6"/>
       <c r="G110" s="6"/>
       <c r="H110" s="13" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J110" s="6"/>
       <c r="K110" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="L110" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M110" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N110" s="13">
         <v>28830</v>
@@ -9250,37 +9236,37 @@
     </row>
     <row r="111" s="2" customFormat="1" spans="1:14">
       <c r="A111" s="6" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="F111" s="6"/>
       <c r="G111" s="6"/>
       <c r="H111" s="13" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J111" s="6"/>
       <c r="K111" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="L111" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M111" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N111" s="13">
         <v>28906</v>
@@ -9288,37 +9274,37 @@
     </row>
     <row r="112" s="2" customFormat="1" spans="1:14">
       <c r="A112" s="6" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F112" s="6"/>
       <c r="G112" s="6"/>
       <c r="H112" s="13" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J112" s="6"/>
       <c r="K112" s="6" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L112" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M112" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N112" s="13">
         <v>30156</v>
@@ -9326,37 +9312,37 @@
     </row>
     <row r="113" s="2" customFormat="1" spans="1:14">
       <c r="A113" s="6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F113" s="6"/>
       <c r="G113" s="6"/>
       <c r="H113" s="13" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J113" s="6"/>
       <c r="K113" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="L113" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M113" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N113" s="13">
         <v>41703</v>
@@ -9364,37 +9350,37 @@
     </row>
     <row r="114" s="2" customFormat="1" spans="1:14">
       <c r="A114" s="6" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="F114" s="6"/>
       <c r="G114" s="6"/>
       <c r="H114" s="13" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J114" s="6"/>
       <c r="K114" s="6" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="L114" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M114" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N114" s="13">
         <v>45200</v>
@@ -9402,37 +9388,37 @@
     </row>
     <row r="115" s="2" customFormat="1" spans="1:14">
       <c r="A115" s="6" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="F115" s="6"/>
       <c r="G115" s="6"/>
       <c r="H115" s="13" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J115" s="6"/>
       <c r="K115" s="6" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="L115" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M115" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N115" s="13">
         <v>45200</v>
@@ -9440,37 +9426,37 @@
     </row>
     <row r="116" s="2" customFormat="1" spans="1:14">
       <c r="A116" s="6" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F116" s="6"/>
       <c r="G116" s="6"/>
       <c r="H116" s="13" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J116" s="6"/>
       <c r="K116" s="6" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="L116" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M116" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N116" s="13">
         <v>45340</v>
@@ -9478,225 +9464,225 @@
     </row>
     <row r="117" s="2" customFormat="1" spans="1:14">
       <c r="A117" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
       <c r="H117" s="13" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J117" s="6"/>
       <c r="K117" s="6" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="L117" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M117" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N117" s="13" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="118" s="2" customFormat="1" spans="1:14">
       <c r="A118" s="6" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="F118" s="6"/>
       <c r="G118" s="6"/>
       <c r="H118" s="13" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J118" s="6"/>
       <c r="K118" s="6" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="L118" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M118" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N118" s="13" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="119" s="2" customFormat="1" spans="1:14">
       <c r="A119" s="6" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F119" s="6"/>
       <c r="G119" s="6"/>
       <c r="H119" s="13" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J119" s="6"/>
       <c r="K119" s="6" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="L119" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M119" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N119" s="13" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="120" s="2" customFormat="1" spans="1:14">
       <c r="A120" s="6" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F120" s="6"/>
       <c r="G120" s="6"/>
       <c r="H120" s="13" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J120" s="6"/>
       <c r="K120" s="6" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="L120" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M120" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N120" s="13" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="121" s="2" customFormat="1" spans="1:14">
       <c r="A121" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="E121" s="6" t="s">
         <v>579</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>579</v>
-      </c>
-      <c r="C121" s="6" t="s">
-        <v>579</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>580</v>
-      </c>
-      <c r="E121" s="6" t="s">
-        <v>581</v>
       </c>
       <c r="F121" s="6"/>
       <c r="G121" s="6"/>
       <c r="H121" s="13" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J121" s="6"/>
       <c r="K121" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="L121" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="M121" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="N121" s="13" t="s">
         <v>583</v>
-      </c>
-      <c r="L121" s="6" t="s">
-        <v>584</v>
-      </c>
-      <c r="M121" s="6" t="s">
-        <v>519</v>
-      </c>
-      <c r="N121" s="13" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="122" s="2" customFormat="1" spans="1:14">
       <c r="A122" s="6" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="6" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="F122" s="6"/>
       <c r="G122" s="6"/>
       <c r="H122" s="13" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J122" s="6"/>
       <c r="K122" s="6" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="L122" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M122" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N122" s="13">
         <v>12200</v>
@@ -9704,35 +9690,35 @@
     </row>
     <row r="123" s="2" customFormat="1" ht="16.8" spans="1:14">
       <c r="A123" s="6" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C123" s="6"/>
       <c r="D123" s="6" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F123" s="6"/>
       <c r="G123" s="6"/>
       <c r="H123" s="13" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J123" s="6"/>
       <c r="K123" s="18" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="L123" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M123" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N123" s="13">
         <v>38290</v>
@@ -9740,73 +9726,73 @@
     </row>
     <row r="124" s="2" customFormat="1" spans="1:14">
       <c r="A124" s="6" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="6" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F124" s="6"/>
       <c r="G124" s="6"/>
       <c r="H124" s="13" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J124" s="6"/>
       <c r="K124" s="6" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="L124" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M124" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N124" s="13" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="125" s="2" customFormat="1" spans="1:14">
       <c r="A125" s="6" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F125" s="6"/>
       <c r="G125" s="6"/>
       <c r="H125" s="13" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J125" s="6"/>
       <c r="K125" s="6" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="L125" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M125" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N125" s="13">
         <v>27050</v>
@@ -9814,35 +9800,35 @@
     </row>
     <row r="126" s="2" customFormat="1" spans="1:14">
       <c r="A126" s="6" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="6" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F126" s="6"/>
       <c r="G126" s="6"/>
       <c r="H126" s="13" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J126" s="6"/>
       <c r="K126" s="6" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="L126" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M126" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N126" s="13">
         <v>41057</v>
@@ -9850,37 +9836,37 @@
     </row>
     <row r="127" s="2" customFormat="1" spans="1:14">
       <c r="A127" s="6" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F127" s="6"/>
       <c r="G127" s="6"/>
       <c r="H127" s="13" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J127" s="6"/>
       <c r="K127" s="6" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="L127" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M127" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N127" s="13">
         <v>41057</v>
@@ -9888,111 +9874,111 @@
     </row>
     <row r="128" s="2" customFormat="1" spans="1:14">
       <c r="A128" s="6" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F128" s="6"/>
       <c r="G128" s="6"/>
       <c r="H128" s="13" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J128" s="6"/>
       <c r="K128" s="6" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="L128" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M128" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N128" s="13" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="129" s="2" customFormat="1" spans="1:14">
       <c r="A129" s="6" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="F129" s="6"/>
       <c r="G129" s="6"/>
       <c r="H129" s="13" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J129" s="6"/>
       <c r="K129" s="6" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="L129" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="M129" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N129" s="13" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="130" s="2" customFormat="1" spans="1:14">
       <c r="A130" s="6" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="6" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="F130" s="6"/>
       <c r="G130" s="6"/>
       <c r="H130" s="13" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J130" s="6"/>
       <c r="K130" s="6" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="L130" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M130" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N130" s="13">
         <v>77550</v>
@@ -10016,46 +10002,46 @@
     </row>
     <row r="132" s="2" customFormat="1" spans="1:14">
       <c r="A132" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I132" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J132" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K132" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L132" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M132" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="N132" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
